--- a/business_surveys/027_onion_shed_management_survey--business_surveys.xlsx
+++ b/business_surveys/027_onion_shed_management_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shed_details</t>
+          <t>Shed Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shed_capacity</t>
+          <t>Shed Capacity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>storage_challenges</t>
+          <t>Storage Challenges</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>storage_conditions</t>
+          <t>Storage Conditions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shed_practices</t>
+          <t>Practices</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>training_hours</t>
+          <t>Training Hours</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>training_topics</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>training_topics</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>location_coordinates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Location Coordinates</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>location_coordinates</t>
+          <t>shed_location</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>location_coordinates</t>
+          <t>Shed Location</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shed_location</t>
+          <t>shed_capacity_awareness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>shed_location</t>
+          <t>Shed Capacity Awareness</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>shed_location_coordinates</t>
+          <t>storage_challenges_awareness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>shed_location_coordinates</t>
+          <t>Storage Challenges Awareness</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>shed_capacity_awareness</t>
+          <t>storage_conditions_awareness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>shed_capacity_awareness</t>
+          <t>Storage Conditions Awareness</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shed_location_awareness</t>
+          <t>practices_awareness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>shed_location_awareness</t>
+          <t>Practices Awareness</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shed_capacity</t>
+          <t>training_hours_awareness</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>shed_capacity</t>
+          <t>Training Hours Awareness</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shed_capacity_awareness</t>
+          <t>shed_location_awareness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>shed_capacity_awareness</t>
+          <t>Shed Location Awareness</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>storage_challenges_awareness</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>storage_challenges_awareness</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>storage_conditions_awareness</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>storage_conditions_awareness</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>shed_practices_awareness</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>shed_practices_awareness</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>training_hours_awareness</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>training_hours_awareness</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>shed_location</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>shed_location</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>onion_rot</t>
+          <t>pests</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Onion rot</t>
+          <t>Pests</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pests</t>
+          <t>mold</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pests</t>
+          <t>Mold</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mold</t>
+          <t>water_damage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mold</t>
+          <t>Water damage</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>water_damage</t>
+          <t>onion_rot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Water damage</t>
+          <t>Onion rot</t>
         </is>
       </c>
     </row>
@@ -1288,57 +1173,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Cleaning and disinfection</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>training_topics_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>temperature_control</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Temperature control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>training_topics_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>humidity_control</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Humidity control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>training_topics_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>cleaning_and_disinfection</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Cleaning and disinfection</t>
         </is>
